--- a/kobo/appeals_monitor_subscription.xlsx
+++ b/kobo/appeals_monitor_subscription.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>constraint</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>constraint_message</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>hint</t>
+          <t>appearance</t>
         </is>
       </c>
     </row>
@@ -477,12 +467,6 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Enter your full name</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,21 +489,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>"regex(., '^[a-zA-Z0-9._%+-]+@[a-zA-Z0-9.-]+\.[a-zA-Z]{2,}$')"</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Please enter a valid email address</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Enter the email address where you want to receive appeal summaries</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,37 +513,56 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Enter your organization name</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_multiple sectors</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>sectors_of_interest</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Which sectors are you interested in following?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>select_one yesno</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Do you want to receive email notifications?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -586,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,32 +598,389 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>sectors</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Administration</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>sectors</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>cva</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cash and Vouchers Assistance (CVA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>communications</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Communications</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cea</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Community Engagement and Accountability (CEA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>digital_systems</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Digital Systems, Tools &amp; Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>emergency_needs_assessment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Emergency Needs Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>humanitarian_diplomacy</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Humanitarian Diplomacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>information_management</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Information Management (IM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>livelihoods</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Livelihoods and Basic Needs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>migration</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>operations_management</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operations Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pmer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Planning, Monitoring, Evaluation and Reporting (PMER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pgi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Protection, Gender, and Inclusion (PGI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>relief</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Relief</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>risk_management</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shelter</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Shelter</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>strategic_partnerships</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Strategic Partnerships and Resource Mobilisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sectors</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wash</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Water, Sanitation and Hygiene (WASH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>yesno</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>yesno</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -651,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,11 +1011,6 @@
           <t>form_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -680,11 +1021,6 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>appeals_monitor_subscription</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>

--- a/kobo/appeals_monitor_subscription.xlsx
+++ b/kobo/appeals_monitor_subscription.xlsx
@@ -466,7 +466,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -489,7 +488,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,7 +510,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -562,7 +559,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -575,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,12 +599,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>cva</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Cash and Vouchers Assistance (CVA)</t>
         </is>
       </c>
     </row>
@@ -620,12 +616,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>cva</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cash and Vouchers Assistance (CVA)</t>
+          <t>Communications</t>
         </is>
       </c>
     </row>
@@ -637,12 +633,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>cea</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Community Engagement and Accountability (CEA)</t>
         </is>
       </c>
     </row>
@@ -654,12 +650,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cea</t>
+          <t>digital_systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Community Engagement and Accountability (CEA)</t>
+          <t>Digital Systems, Tools &amp; Information Technology</t>
         </is>
       </c>
     </row>
@@ -671,12 +667,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>digital_systems</t>
+          <t>green_response</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Digital Systems, Tools &amp; Information Technology</t>
+          <t>Green Response (GR)</t>
         </is>
       </c>
     </row>
@@ -688,12 +684,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>emergency_needs_assessment</t>
+          <t>health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emergency Needs Assessment</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -705,12 +701,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>humanitarian_diplomacy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Humanitarian Diplomacy</t>
         </is>
       </c>
     </row>
@@ -722,12 +718,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>humanitarian_diplomacy</t>
+          <t>information_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Humanitarian Diplomacy</t>
+          <t>Information Management (IM)</t>
         </is>
       </c>
     </row>
@@ -739,12 +735,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>information_management</t>
+          <t>livelihoods</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Information Management (IM)</t>
+          <t>Livelihoods and Basic Needs</t>
         </is>
       </c>
     </row>
@@ -756,12 +752,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>livelihoods</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Livelihoods and Basic Needs</t>
+          <t>Logistics</t>
         </is>
       </c>
     </row>
@@ -773,12 +769,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>migration</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Migration</t>
         </is>
       </c>
     </row>
@@ -790,12 +786,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>migration</t>
+          <t>operations_management</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Operations Management</t>
         </is>
       </c>
     </row>
@@ -807,12 +803,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>operations_management</t>
+          <t>pmer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Operations Management</t>
+          <t>Planning, Monitoring, Evaluation and Reporting (PMER)</t>
         </is>
       </c>
     </row>
@@ -824,12 +820,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pmer</t>
+          <t>pgi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Planning, Monitoring, Evaluation and Reporting (PMER)</t>
+          <t>Protection, Gender, and Inclusion (PGI)</t>
         </is>
       </c>
     </row>
@@ -841,12 +837,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pgi</t>
+          <t>relief</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Protection, Gender, and Inclusion (PGI)</t>
+          <t>Relief</t>
         </is>
       </c>
     </row>
@@ -858,12 +854,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>relief</t>
+          <t>security</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Relief</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -875,12 +871,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>risk_management</t>
+          <t>shelter</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Shelter</t>
         </is>
       </c>
     </row>
@@ -892,12 +888,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>strategic_partnerships</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Strategic Partnerships and Resource Mobilisation</t>
         </is>
       </c>
     </row>
@@ -909,78 +905,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>shelter</t>
+          <t>wash</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Water, Sanitation and Hygiene (WASH)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sectors</t>
+          <t>yesno</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>strategic_partnerships</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Strategic Partnerships and Resource Mobilisation</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sectors</t>
+          <t>yesno</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wash</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>Water, Sanitation and Hygiene (WASH)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>yesno</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>yesno</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/kobo/appeals_monitor_subscription.xlsx
+++ b/kobo/appeals_monitor_subscription.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodekruis-my.sharepoint.com/personal/jmargutti_redcross_nl/Documents/Rode Kruis/510/appeals-monitor/kobo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_25461DF59C776CC308D42902D282304B858B4371" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA5C5587-FA04-4D4B-B7F6-17B866D072B5}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" r:id="rId3"/>
+    <sheet r:id="rId1" sheetId="1" name="survey"/>
+    <sheet r:id="rId2" sheetId="2" name="choices"/>
+    <sheet r:id="rId3" sheetId="3" name="settings"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -186,6 +180,9 @@
     <t>required</t>
   </si>
   <si>
+    <t>relevant</t>
+  </si>
+  <si>
     <t>appearance</t>
   </si>
   <si>
@@ -195,72 +192,76 @@
     <t>intro</t>
   </si>
   <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Email address</t>
-  </si>
-  <si>
-    <t>select_multiple sectors</t>
-  </si>
-  <si>
-    <t>sectors_of_interest</t>
-  </si>
-  <si>
-    <t>Which sectors are you interested in following?</t>
-  </si>
-  <si>
-    <t>minimal</t>
+    <t>Sign up to receive email notifications when new IFRC appeals (DREF, Emergency Appeals, Operational Strategies) are published. Choose the sectors you're interested in (e.g. CVA, WASH, Shelter) and you'll receive only the updates relevant to you. You can update your preferences or opt out at any time by re-submitting this form.</t>
   </si>
   <si>
     <t>select_one yesno</t>
   </si>
   <si>
     <t>active</t>
-  </si>
-  <si>
-    <t>Please note: you will only receive notifications for appeals that include interventions in your selected sector(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Do you consent to receiving email notifications related to IFRC appeals?
 </t>
   </si>
   <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>${active} = yes</t>
-  </si>
-  <si>
-    <t>${active} = no</t>
+    <t>Choose 'no' if you previously signed up and would like to opt out.</t>
+  </si>
+  <si>
+    <t>text</t>
   </si>
   <si>
     <t>First name</t>
   </si>
   <si>
-    <t>Sign up to receive email notifications when new IFRC appeals (DREF, Emergency Appeals, Operational Strategies) are published. Choose the sectors you're interested in (e.g. CVA, WASH, Shelter) and you'll receive only the updates relevant to you. You can update your preferences or opt out at any time by re-submitting this form.</t>
-  </si>
-  <si>
-    <t>Choose 'no' if you previously signed up and would like to opt out.</t>
+    <t>${active} = 'yes'</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>Email address</t>
+  </si>
+  <si>
+    <t>select_multiple sectors</t>
+  </si>
+  <si>
+    <t>sectors_of_interest</t>
+  </si>
+  <si>
+    <t>Which sectors are you interested in following?</t>
+  </si>
+  <si>
+    <t>Please note: you will only receive notifications for appeals that include interventions in your selected sector(s).</t>
+  </si>
+  <si>
+    <t>minimal</t>
   </si>
   <si>
     <t>Thank you for letting us know, after you submitted this form you will not receive emails anymore.</t>
+  </si>
+  <si>
+    <t>${active} = 'no'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -271,7 +272,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -283,24 +291,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="7">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -311,10 +330,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -352,71 +371,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -444,7 +463,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -467,11 +486,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -480,13 +499,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -496,7 +515,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -505,7 +524,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -514,7 +533,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -522,10 +541,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -590,145 +609,160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="13.578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.47265625" customWidth="1"/>
-    <col min="7" max="7" width="13.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="343.5">
+      <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="84" customFormat="1" s="4">
+      <c r="A3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="57.75">
+      <c r="A6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="109.5">
+      <c r="A7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="F7" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" t="s">
-        <v>70</v>
-      </c>
+      <c r="G7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -736,255 +770,257 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" t="s">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" t="s">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -994,29 +1030,30 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/kobo/appeals_monitor_subscription.xlsx
+++ b/kobo/appeals_monitor_subscription.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="survey"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="76">
   <si>
     <t>form_title</t>
   </si>
@@ -24,7 +24,7 @@
     <t>form_id</t>
   </si>
   <si>
-    <t>Appeals Monitor Subscription</t>
+    <t>Appeals Monitor</t>
   </si>
   <si>
     <t>appeals_monitor_subscription</t>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>minimal</t>
+  </si>
+  <si>
+    <t>optout</t>
   </si>
   <si>
     <t>Thank you for letting us know, after you submitted this form you will not receive emails anymore.</t>
@@ -747,20 +750,20 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="109.5">
       <c r="A7" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="1"/>
     </row>
@@ -1037,8 +1040,8 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="17.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="27.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
